--- a/4_VERIFICATION_VALIDATION/Verification-Test-Cases.xlsx
+++ b/4_VERIFICATION_VALIDATION/Verification-Test-Cases.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,23 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,8 +429,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -431,44 +457,44 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Objective</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Expected Outcomes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -478,37 +504,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>VER-001</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Active IR Motion Detection</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Verify motion sensor detects movement within spec</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, sensor calibrated, test area clear</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Place test object 2m in front of sensor
 2. Move object across field of view
@@ -516,9 +542,12 @@
 4. Verify alert threshold met</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Motion event detected &lt;500ms; hub logs timestamp and sensor ID</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1. Motion event detected &lt;500ms
+2. hub logs timestamp and sensor ID
+3. Step completed as expected
+4. Verification successful</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -528,37 +557,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>VER-002</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Motion Sensor False Alarm Rate</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Verify false alarm rate &lt;2% per spec</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, sensor deployed in living room, 1-hour observation period</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Enable motion sensor
 2. Operate normally (no personnel)
@@ -566,9 +595,12 @@
 4. Calculate false alarm rate</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>False alarm rate ≤2%; no phantom triggers</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1. False alarm rate ≤2%
+2. no phantom triggers
+3. Step completed as expected
+4. Step completed as expected</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -578,37 +610,37 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>VER-003</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Motion Detection with Failover</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Verify motion alerts work when WiFi down</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Hub with battery backup, WiFi disabled, cellular ready</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect WiFi
 2. Trigger motion sensor
@@ -616,9 +648,12 @@
 4. Verify cellular alert sent</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Local alarm triggers &lt;1s; cellular alert queued; no alert loss</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1. Local alarm triggers &lt;1s
+2. cellular alert queued
+3. no alert loss
+4. Verification successful</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -628,37 +663,37 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>VER-004</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Magnetic Door Sensor Detection</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Verify door/window sensor detects open state</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, door sensor installed on front door</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Open door 5cm
 2. Monitor hub event log
@@ -666,9 +701,12 @@
 4. Verify state change logged</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Door open event detected &lt;100ms; state change logged</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1. Door open event detected &lt;100ms
+2. state change logged
+3. Step completed as expected
+4. Verification successful</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -678,46 +716,48 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>VER-005</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Door Sensor False Triggers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Verify door sensor does not false trigger on vibration</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, door sensor installed, door closed</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Vibrate door frame (tap, traffic vibration)
 2. Monitor event log for 5 minutes
 3. Verify no false open events</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>No spurious open events detected</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1. No spurious open events detected
+2. Step completed as expected
+3. Verification successful</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -727,37 +767,37 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>VER-006</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Door Sensor Battery Life</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Verify door sensor battery lasts 5+ years</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Door sensor deployed, hub monitoring battery voltage</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. Deploy sensor
 2. Monitor battery voltage weekly for 4 weeks
@@ -765,9 +805,12 @@
 4. Extrapolate to 5-year life</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Battery maintains &gt;90% capacity after 12 weeks; &gt;40 years extrapolated life</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1. Battery maintains &gt;90% capacity after 12 weeks
+2. &gt;40 years extrapolated life
+3. Step completed as expected
+4. Step completed as expected</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -777,46 +820,48 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>VER-007</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Water Leak Detection Sensitivity</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Verify water sensor detects leak &lt;500ms</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, water sensor installed under kitchen sink</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. Drip water onto sensor cord
 2. Monitor hub event log
 3. Measure detection latency</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Water leak event detected &lt;500ms after water contact</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1. Water leak event detected &lt;500ms after water contact
+2. Step completed as expected
+3. Step completed as expected</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -826,37 +871,37 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>VER-008</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Water Leak Auto-Shutoff Valve</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Verify automatic water valve closes on leak detect</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, water sensor + shutoff valve configured, water supply on</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. Trigger water sensor
 2. Monitor valve state change
@@ -864,9 +909,12 @@
 4. Check hub logs</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Shutoff valve closes &lt;2 seconds after leak detected; water flow halts</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1. Shutoff valve closes &lt;2 seconds after leak detected
+2. water flow halts
+3. Verification successful
+4. Check completed</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -876,37 +924,37 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>VER-009</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>PoE Camera 4K Video Recording</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Verify PoE camera records 4K at 30fps locally</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, PoE camera connected, storage available</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. Start video capture
 2. Run for 5 minutes
@@ -914,9 +962,12 @@
 4. Verify local storage</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Video recorded at 4K (3840x2160) 30fps; file stored locally</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1. Video recorded at 4K (3840x2160) 30fps
+2. file stored locally
+3. Check completed
+4. Verification successful</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -926,37 +977,37 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>VER-010</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>PoE Camera Night Vision</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Verify IR night vision activates in low light</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, PoE camera, dark room setup</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. Enable night mode
 2. Dim room to &lt;5 lux
@@ -964,9 +1015,12 @@
 4. Verify IR LED activation</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>IR LEDs activate; image visible in &lt;5 lux; quality acceptable</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1. IR LEDs activate
+2. image visible in &lt;5 lux
+3. quality acceptable
+4. Verification successful</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -976,37 +1030,37 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>VER-011</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>PoE Camera 30-Day Local Storage</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Verify 2TB SSD holds 30 days of 4K video</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, 2TB SSD installed, PoE camera recording</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. Calculate storage requirement: 4K 30fps = ~400 GB/hour
 2. Start 24/7 recording
@@ -1014,9 +1068,12 @@
 4. Verify not full after 30 days</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Storage reaches ~85% capacity after 30 days; no video loss</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1. Storage reaches ~85% capacity after 30 days
+2. no video loss
+3. Step completed as expected
+4. Verification successful</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1026,37 +1083,37 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>VER-012</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>PoE Camera Motion Detection</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Verify motion detection triggers recording priority</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, PoE camera, motion detection enabled</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. Enable motion detection
 2. Walk past camera
@@ -1064,9 +1121,12 @@
 4. Verify priority flag set</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Motion detected &lt;500ms; priority tag applied to recording segment</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1. Motion detected &lt;500ms
+2. priority tag applied to recording segment
+3. Step completed as expected
+4. Verification successful</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1076,37 +1136,37 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>VER-013</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>WiFi Smart Lock Integration</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Verify lock responds to hub commands &lt;5s</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, WiFi smart lock configured, batteries charged</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. Send lock command via hub app
 2. Measure response time
@@ -1114,9 +1174,12 @@
 4. Log command in hub</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Lock state changes &lt;5 seconds; hub confirms command executed</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1. Lock state changes &lt;5 seconds
+2. hub confirms command executed
+3. Verification successful
+4. Step completed as expected</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1126,37 +1189,37 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>VER-014</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>WiFi Smart Lock Manual Override</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Verify manual key still works during network down</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, WiFi smart lock, WiFi disabled</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. Disable WiFi
 2. Use physical key to lock/unlock
@@ -1164,9 +1227,12 @@
 4. Re-enable WiFi</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Physical key operation unaffected; hub resumes tracking after WiFi restored</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1. Physical key operation unaffected
+2. hub resumes tracking after WiFi restored
+3. Verification successful
+4. Step completed as expected</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1176,37 +1242,37 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>VER-015</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Smart Light Brightness Control</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Verify lights respond to automation rules</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, Philips Hue lights configured, automation rule created</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. Create rule: arm=disarm all lights
 2. Send disarm command
@@ -1214,9 +1280,12 @@
 4. Verify brightness matches rule</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Lights turn on/off per rule &lt;3 seconds; brightness level correct</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1. Lights turn on/off per rule &lt;3 seconds
+2. brightness level correct
+3. Step completed as expected
+4. Verification successful</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1226,37 +1295,37 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>VER-016</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Smart Outlet Relay Control</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Verify outlet switches on command</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, Wemo outlet configured, lamp plugged in</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. Send on command to outlet
 2. Measure response time
@@ -1264,9 +1333,12 @@
 4. Repeat for off command</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Outlet switches on/off &lt;3 seconds; power state confirmed</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1. Outlet switches on/off &lt;3 seconds
+2. power state confirmed
+3. Verification successful
+4. Step completed as expected</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1276,37 +1348,37 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>VER-017</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Controller Offline Operation</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Verify controllers work during cloud outage</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, controllers configured, cloud unavailable</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. Disable cloud connectivity
 2. Send controller commands via hub
@@ -1314,9 +1386,12 @@
 4. Verify local operation succeeds</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Controllers respond to local commands; no cloud dependency for core function</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1. Controllers respond to local commands
+2. no cloud dependency for core function
+3. Step completed as expected
+4. Verification successful</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1326,37 +1401,37 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>VER-018</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Siren Audio Alert</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Verify alarm siren reaches 100dB at 1m</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, siren connected, sound meter available</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. Trigger alarm mode
 2. Measure siren output at 1 meter
@@ -1364,9 +1439,12 @@
 4. Check audio spectrum</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Siren output ≥100 dB SPL at 1m; sustained for alarm duration</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1. Siren output ≥100 dB SPL at 1m
+2. sustained for alarm duration
+3. Verification successful
+4. Check completed</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1376,37 +1454,37 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>VER-019</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Push Notification Delivery</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Verify mobile app receives alerts &lt;10s on WiFi</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, mobile app installed, WiFi active</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. Trigger motion sensor
 2. Monitor hub timestamp
@@ -1414,9 +1492,12 @@
 4. Calculate latency</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Notification received &lt;10 seconds on WiFi; &lt;15s on cellular</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1. Notification received &lt;10 seconds on WiFi
+2. &lt;15s on cellular
+3. Step completed as expected
+4. Step completed as expected</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1426,37 +1507,37 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>VER-020</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Multi-User Notification</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Verify all authorized users receive alert</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, 3+ users configured with different roles</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Trigger security event
 2. Monitor notifications for each user
@@ -1464,9 +1545,12 @@
 4. Confirm ACL honored</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>All authorized users receive alert; unauthorized users do not</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1. All authorized users receive alert
+2. unauthorized users do not
+3. Verification successful
+4. Step completed as expected</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1476,37 +1560,37 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>VER-021</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Authentication MFA Verification</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Verify MFA code required for admin access</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, MFA enabled for admin account</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Attempt admin login
 2. Verify MFA prompt appears
@@ -1516,9 +1600,14 @@
 6. Verify login succeeds</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Invalid MFA rejected; valid MFA grants access; 2 of 3 factors required</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1. Invalid MFA rejected
+2. valid MFA grants access
+3. 2 of 3 factors required
+4. Verification successful
+5. Step completed as expected
+6. Verification successful</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1528,37 +1617,37 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>VER-022</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Role-Based Access Control</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Verify guest role cannot change settings</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, guest user account created</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Login as guest
 2. Attempt to change security settings
@@ -1566,9 +1655,12 @@
 4. Verify action blocked</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Guest cannot modify settings; admin notified of attempt; audit logged</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1. Guest cannot modify settings
+2. admin notified of attempt
+3. audit logged
+4. Verification successful</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1578,37 +1670,37 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>VER-023</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Session Timeout</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Verify remote session expires after 30 minutes</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, user logged in remotely</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Login to hub remotely
 2. Observe activity timeout after 30 min
@@ -1616,9 +1708,12 @@
 4. Verify re-authentication required</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Session expires after 30 min inactivity; re-login required; no persistent connection</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1. Session expires after 30 min inactivity
+2. re-login required
+3. no persistent connection
+4. Verification successful</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1628,37 +1723,37 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>VER-024</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Password Complexity Enforcement</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Verify weak passwords rejected</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, account creation enabled</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Attempt password: '123456'
 2. Verify rejected
@@ -1666,9 +1761,12 @@
 4. Verify accepted</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Weak password rejected; strong password accepted per NIST guidelines</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1. Weak password rejected
+2. strong password accepted per NIST guidelines
+3. Step completed as expected
+4. Verification successful</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1678,37 +1776,37 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>VER-025</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Encryption in Transit</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Verify HTTPS/TLS 1.2 for cloud communications</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Hub configured for cloud sync</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Capture network traffic during cloud sync
 2. Analyze packet encryption
@@ -1716,9 +1814,12 @@
 4. Check certificate chain</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>All cloud traffic encrypted TLS 1.2+; certificate chain valid</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1. All cloud traffic encrypted TLS 1.2+
+2. certificate chain valid
+3. Verification successful
+4. Check completed</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1728,37 +1829,37 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>VER-026</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Data Privacy - No Logs Shared</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Verify video not sent to cloud without consent</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, cloud disabled in settings</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. Disable cloud upload setting
 2. Trigger camera recording
@@ -1766,9 +1867,12 @@
 4. Verify no outbound video flow</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>No video data transmitted to cloud; only metadata cached locally</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1. No video data transmitted to cloud
+2. only metadata cached locally
+3. Step completed as expected
+4. Verification successful</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1778,37 +1882,37 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>VER-027</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>WiFi to Cellular Failover</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Verify &lt;30s switchover when WiFi lost</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Hub with WiFi and cellular, WiFi connected initially</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. Power on hub with WiFi
 2. Disconnect WiFi (unplug router)
@@ -1817,9 +1921,13 @@
 5. Verify alert sent via cellular</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Failover to cellular &lt;30 seconds; alert queued during transition; no alert loss</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>1. Failover to cellular &lt;30 seconds
+2. alert queued during transition
+3. no alert loss
+4. Step completed as expected
+5. Verification successful</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1829,37 +1937,37 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>VER-028</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>LoRaWAN Radio Mesh Range</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Verify 500m range in open space</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Hub with LoRaWAN gateway, test sensor, open field</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Deploy sensor 500m from hub
 2. Trigger sensor event
@@ -1867,9 +1975,12 @@
 4. Verify event detected</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sensor event received at 500m range; latency &lt;1000ms</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>1. Sensor event received at 500m range
+2. latency &lt;1000ms
+3. Step completed as expected
+4. Verification successful</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1879,37 +1990,37 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>VER-029</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>System Health Self-Test</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Verify daily self-test executed and logged</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, self-test scheduled daily at 2am</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Monitor for 24 hours
 2. Observe self-test execution at scheduled time
@@ -1917,9 +2028,12 @@
 4. Verify all subsystems tested</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Self-test executes daily; all subsystems report pass/fail; logs retained</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>1. Self-test executes daily
+2. all subsystems report pass/fail
+3. logs retained
+4. Verification successful</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1929,37 +2043,37 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>VER-030</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Hub Boot Recovery</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Verify hub resumes operation after power loss</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Hub powered on, event in progress, power cut</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. Power down hub during active event
 2. Wait 10 seconds
@@ -1968,9 +2082,13 @@
 5. Verify operational within 2 minutes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Hub boots successfully; resumes monitoring; cached events not lost</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>1. Hub boots successfully
+2. resumes monitoring
+3. cached events not lost
+4. Step completed as expected
+5. Verification successful</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1979,63 +2097,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notes: </t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>- All test cases map to specific SysRS requirements (REQ-001+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>- Priority: P0=Critical</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> P1=High</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> P2=Medium</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> P3=Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>- Type: Integration tests verify component interactions; unit tests for individual components included in integration tests</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>- Each test designed to pass/fail unambiguously</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>- Tests include both happy path and error conditions</t>
-        </is>
-      </c>
-    </row>
+    <row r="35"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4_VERIFICATION_VALIDATION/Verification-Test-Cases.xlsx
+++ b/4_VERIFICATION_VALIDATION/Verification-Test-Cases.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -442,62 +442,46 @@
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Verification Test Cases - Smart Home Security System</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>IEEE 29148:2018 | Phase 4 Verification &amp; Validation</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Test ID</t>
+          <t>Test Case Name</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Test Name</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Precondition</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Expected Outcomes</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Related Requirement(s)</t>
         </is>
@@ -506,51 +490,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>VER-001</t>
+          <t>VER-001: Active IR Motion Detection</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Active IR Motion Detection</t>
+          <t>Verify motion sensor detects movement within spec</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Verify motion sensor detects movement within spec</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, sensor calibrated, test area clear</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, sensor calibrated, test area clear</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Place test object 2m in front of sensor
-2. Move object across field of view
-3. Monitor hub event log
-4. Verify alert threshold met</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1. Motion event detected &lt;500ms
-2. hub logs timestamp and sensor ID
-3. Step completed as expected
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+          <t>Step 1: Place test object 2m in front of sensor
+Step 2: Move object across field of view
+Step 3: Monitor hub event log
+Step 4: Verify alert threshold met</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Motion event detected &lt;500ms
+Expected Outcome 2: hub logs timestamp and sensor ID
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>REQ-010-011</t>
         </is>
@@ -559,51 +538,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>VER-002</t>
+          <t>VER-002: Motion Sensor False Alarm Rate</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Motion Sensor False Alarm Rate</t>
+          <t>Verify false alarm rate &lt;2% per spec</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Verify false alarm rate &lt;2% per spec</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, sensor deployed in living room, 1-hour observation period</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, sensor deployed in living room, 1-hour observation period</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Enable motion sensor
-2. Operate normally (no personnel)
-3. Count false alarms over 60 minutes
-4. Calculate false alarm rate</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1. False alarm rate ≤2%
-2. no phantom triggers
-3. Step completed as expected
-4. Step completed as expected</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+          <t>Step 1: Enable motion sensor
+Step 2: Operate normally (no personnel)
+Step 3: Count false alarms over 60 minutes
+Step 4: Calculate false alarm rate</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: False alarm rate ≤2%
+Expected Outcome 2: no phantom triggers
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Step completed as expected</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>REQ-011</t>
         </is>
@@ -612,51 +586,46 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>VER-003</t>
+          <t>VER-003: Motion Detection with Failover</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Motion Detection with Failover</t>
+          <t>Verify motion alerts work when WiFi down</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Verify motion alerts work when WiFi down</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub with battery backup, WiFi disabled, cellular ready</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Hub with battery backup, WiFi disabled, cellular ready</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect WiFi
-2. Trigger motion sensor
-3. Verify local alarm triggers
-4. Verify cellular alert sent</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1. Local alarm triggers &lt;1s
-2. cellular alert queued
-3. no alert loss
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+          <t>Step 1: Disconnect WiFi
+Step 2: Trigger motion sensor
+Step 3: Verify local alarm triggers
+Step 4: Verify cellular alert sent</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Local alarm triggers &lt;1s
+Expected Outcome 2: cellular alert queued
+Expected Outcome 3: no alert loss
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>REQ-010-011; REQ-124</t>
         </is>
@@ -665,51 +634,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>VER-004</t>
+          <t>VER-004: Magnetic Door Sensor Detection</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Magnetic Door Sensor Detection</t>
+          <t>Verify door/window sensor detects open state</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Verify door/window sensor detects open state</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, door sensor installed on front door</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, door sensor installed on front door</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1. Open door 5cm
-2. Monitor hub event log
-3. Close door
-4. Verify state change logged</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1. Door open event detected &lt;100ms
-2. state change logged
-3. Step completed as expected
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+          <t>Step 1: Open door 5cm
+Step 2: Monitor hub event log
+Step 3: Close door
+Step 4: Verify state change logged</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Door open event detected &lt;100ms
+Expected Outcome 2: state change logged
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>REQ-020-021</t>
         </is>
@@ -718,49 +682,44 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>VER-005</t>
+          <t>VER-005: Door Sensor False Triggers</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Door Sensor False Triggers</t>
+          <t>Verify door sensor does not false trigger on vibration</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Verify door sensor does not false trigger on vibration</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, door sensor installed, door closed</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, door sensor installed, door closed</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1. Vibrate door frame (tap, traffic vibration)
-2. Monitor event log for 5 minutes
-3. Verify no false open events</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1. No spurious open events detected
-2. Step completed as expected
-3. Verification successful</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+          <t>Step 1: Vibrate door frame (tap, traffic vibration)
+Step 2: Monitor event log for 5 minutes
+Step 3: Verify no false open events</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: No spurious open events detected
+Expected Outcome 2: Step completed as expected
+Expected Outcome 3: Verification successful</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>REQ-022</t>
         </is>
@@ -769,51 +728,46 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>VER-006</t>
+          <t>VER-006: Door Sensor Battery Life</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Door Sensor Battery Life</t>
+          <t>Verify door sensor battery lasts 5+ years</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Verify door sensor battery lasts 5+ years</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Door sensor deployed, hub monitoring battery voltage</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Door sensor deployed, hub monitoring battery voltage</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1. Deploy sensor
-2. Monitor battery voltage weekly for 4 weeks
-3. Calculate discharge rate
-4. Extrapolate to 5-year life</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1. Battery maintains &gt;90% capacity after 12 weeks
-2. &gt;40 years extrapolated life
-3. Step completed as expected
-4. Step completed as expected</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+          <t>Step 1: Deploy sensor
+Step 2: Monitor battery voltage weekly for 4 weeks
+Step 3: Calculate discharge rate
+Step 4: Extrapolate to 5-year life</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Battery maintains &gt;90% capacity after 12 weeks
+Expected Outcome 2: &gt;40 years extrapolated life
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Step completed as expected</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>REQ-023-024</t>
         </is>
@@ -822,49 +776,44 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>VER-007</t>
+          <t>VER-007: Water Leak Detection Sensitivity</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Water Leak Detection Sensitivity</t>
+          <t>Verify water sensor detects leak &lt;500ms</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Verify water sensor detects leak &lt;500ms</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, water sensor installed under kitchen sink</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, water sensor installed under kitchen sink</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1. Drip water onto sensor cord
-2. Monitor hub event log
-3. Measure detection latency</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1. Water leak event detected &lt;500ms after water contact
-2. Step completed as expected
-3. Step completed as expected</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+          <t>Step 1: Drip water onto sensor cord
+Step 2: Monitor hub event log
+Step 3: Measure detection latency</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Water leak event detected &lt;500ms after water contact
+Expected Outcome 2: Step completed as expected
+Expected Outcome 3: Step completed as expected</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>REQ-030-031</t>
         </is>
@@ -873,51 +822,46 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>VER-008</t>
+          <t>VER-008: Water Leak Auto-Shutoff Valve</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Water Leak Auto-Shutoff Valve</t>
+          <t>Verify automatic water valve closes on leak detect</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Verify automatic water valve closes on leak detect</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, water sensor + shutoff valve configured, water supply on</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, water sensor + shutoff valve configured, water supply on</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1. Trigger water sensor
-2. Monitor valve state change
-3. Verify water flow stops
-4. Check hub logs</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1. Shutoff valve closes &lt;2 seconds after leak detected
-2. water flow halts
-3. Verification successful
-4. Check completed</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
+          <t>Step 1: Trigger water sensor
+Step 2: Monitor valve state change
+Step 3: Verify water flow stops
+Step 4: Check hub logs</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Shutoff valve closes &lt;2 seconds after leak detected
+Expected Outcome 2: water flow halts
+Expected Outcome 3: Verification successful
+Expected Outcome 4: Check completed</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>REQ-032-033</t>
         </is>
@@ -926,51 +870,46 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>VER-009</t>
+          <t>VER-009: PoE Camera 4K Video Recording</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PoE Camera 4K Video Recording</t>
+          <t>Verify PoE camera records 4K at 30fps locally</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Verify PoE camera records 4K at 30fps locally</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, PoE camera connected, storage available</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, PoE camera connected, storage available</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1. Start video capture
-2. Run for 5 minutes
-3. Check resolution and frame rate
-4. Verify local storage</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1. Video recorded at 4K (3840x2160) 30fps
-2. file stored locally
-3. Check completed
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+          <t>Step 1: Start video capture
+Step 2: Run for 5 minutes
+Step 3: Check resolution and frame rate
+Step 4: Verify local storage</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Video recorded at 4K (3840x2160) 30fps
+Expected Outcome 2: file stored locally
+Expected Outcome 3: Check completed
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>REQ-040-041</t>
         </is>
@@ -979,51 +918,46 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>VER-010</t>
+          <t>VER-010: PoE Camera Night Vision</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PoE Camera Night Vision</t>
+          <t>Verify IR night vision activates in low light</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Verify IR night vision activates in low light</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, PoE camera, dark room setup</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, PoE camera, dark room setup</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1. Enable night mode
-2. Dim room to &lt;5 lux
-3. Capture image
-4. Verify IR LED activation</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1. IR LEDs activate
-2. image visible in &lt;5 lux
-3. quality acceptable
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+          <t>Step 1: Enable night mode
+Step 2: Dim room to &lt;5 lux
+Step 3: Capture image
+Step 4: Verify IR LED activation</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: IR LEDs activate
+Expected Outcome 2: image visible in &lt;5 lux
+Expected Outcome 3: quality acceptable
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>REQ-042</t>
         </is>
@@ -1032,51 +966,46 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>VER-011</t>
+          <t>VER-011: PoE Camera 30-Day Local Storage</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>PoE Camera 30-Day Local Storage</t>
+          <t>Verify 2TB SSD holds 30 days of 4K video</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Verify 2TB SSD holds 30 days of 4K video</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, 2TB SSD installed, PoE camera recording</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, 2TB SSD installed, PoE camera recording</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1. Calculate storage requirement: 4K 30fps = ~400 GB/hour
-2. Start 24/7 recording
-3. Monitor storage usage for 30 days
-4. Verify not full after 30 days</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1. Storage reaches ~85% capacity after 30 days
-2. no video loss
-3. Step completed as expected
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+          <t>Step 1: Calculate storage requirement: 4K 30fps = ~400 GB/hour
+Step 2: Start 24/7 recording
+Step 3: Monitor storage usage for 30 days
+Step 4: Verify not full after 30 days</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Storage reaches ~85% capacity after 30 days
+Expected Outcome 2: no video loss
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>REQ-043-044</t>
         </is>
@@ -1085,51 +1014,46 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>VER-012</t>
+          <t>VER-012: PoE Camera Motion Detection</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PoE Camera Motion Detection</t>
+          <t>Verify motion detection triggers recording priority</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Verify motion detection triggers recording priority</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, PoE camera, motion detection enabled</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, PoE camera, motion detection enabled</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1. Enable motion detection
-2. Walk past camera
-3. Monitor hub event log
-4. Verify priority flag set</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1. Motion detected &lt;500ms
-2. priority tag applied to recording segment
-3. Step completed as expected
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+          <t>Step 1: Enable motion detection
+Step 2: Walk past camera
+Step 3: Monitor hub event log
+Step 4: Verify priority flag set</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Motion detected &lt;500ms
+Expected Outcome 2: priority tag applied to recording segment
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>REQ-045-046</t>
         </is>
@@ -1138,51 +1062,46 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>VER-013</t>
+          <t>VER-013: WiFi Smart Lock Integration</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>WiFi Smart Lock Integration</t>
+          <t>Verify lock responds to hub commands &lt;5s</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Verify lock responds to hub commands &lt;5s</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, WiFi smart lock configured, batteries charged</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, WiFi smart lock configured, batteries charged</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1. Send lock command via hub app
-2. Measure response time
-3. Verify door lock state changes
-4. Log command in hub</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1. Lock state changes &lt;5 seconds
-2. hub confirms command executed
-3. Verification successful
-4. Step completed as expected</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+          <t>Step 1: Send lock command via hub app
+Step 2: Measure response time
+Step 3: Verify door lock state changes
+Step 4: Log command in hub</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Lock state changes &lt;5 seconds
+Expected Outcome 2: hub confirms command executed
+Expected Outcome 3: Verification successful
+Expected Outcome 4: Step completed as expected</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>REQ-065-066</t>
         </is>
@@ -1191,51 +1110,46 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>VER-014</t>
+          <t>VER-014: WiFi Smart Lock Manual Override</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>WiFi Smart Lock Manual Override</t>
+          <t>Verify manual key still works during network down</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Verify manual key still works during network down</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, WiFi smart lock, WiFi disabled</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, WiFi smart lock, WiFi disabled</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1. Disable WiFi
-2. Use physical key to lock/unlock
-3. Verify mechanical function works
-4. Re-enable WiFi</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1. Physical key operation unaffected
-2. hub resumes tracking after WiFi restored
-3. Verification successful
-4. Step completed as expected</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+          <t>Step 1: Disable WiFi
+Step 2: Use physical key to lock/unlock
+Step 3: Verify mechanical function works
+Step 4: Re-enable WiFi</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Physical key operation unaffected
+Expected Outcome 2: hub resumes tracking after WiFi restored
+Expected Outcome 3: Verification successful
+Expected Outcome 4: Step completed as expected</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>REQ-067</t>
         </is>
@@ -1244,51 +1158,46 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>VER-015</t>
+          <t>VER-015: Smart Light Brightness Control</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Smart Light Brightness Control</t>
+          <t>Verify lights respond to automation rules</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Verify lights respond to automation rules</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, Philips Hue lights configured, automation rule created</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, Philips Hue lights configured, automation rule created</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1. Create rule: arm=disarm all lights
-2. Send disarm command
-3. Monitor light state
-4. Verify brightness matches rule</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1. Lights turn on/off per rule &lt;3 seconds
-2. brightness level correct
-3. Step completed as expected
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+          <t>Step 1: Create rule: arm=disarm all lights
+Step 2: Send disarm command
+Step 3: Monitor light state
+Step 4: Verify brightness matches rule</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Lights turn on/off per rule &lt;3 seconds
+Expected Outcome 2: brightness level correct
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>REQ-068-069</t>
         </is>
@@ -1297,51 +1206,46 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>VER-016</t>
+          <t>VER-016: Smart Outlet Relay Control</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Smart Outlet Relay Control</t>
+          <t>Verify outlet switches on command</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Verify outlet switches on command</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, Wemo outlet configured, lamp plugged in</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, Wemo outlet configured, lamp plugged in</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1. Send on command to outlet
-2. Measure response time
-3. Verify lamp power
-4. Repeat for off command</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1. Outlet switches on/off &lt;3 seconds
-2. power state confirmed
-3. Verification successful
-4. Step completed as expected</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+          <t>Step 1: Send on command to outlet
+Step 2: Measure response time
+Step 3: Verify lamp power
+Step 4: Repeat for off command</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Outlet switches on/off &lt;3 seconds
+Expected Outcome 2: power state confirmed
+Expected Outcome 3: Verification successful
+Expected Outcome 4: Step completed as expected</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>REQ-070</t>
         </is>
@@ -1350,51 +1254,46 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>VER-017</t>
+          <t>VER-017: Controller Offline Operation</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Controller Offline Operation</t>
+          <t>Verify controllers work during cloud outage</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Verify controllers work during cloud outage</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, controllers configured, cloud unavailable</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, controllers configured, cloud unavailable</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1. Disable cloud connectivity
-2. Send controller commands via hub
-3. Monitor controller response
-4. Verify local operation succeeds</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1. Controllers respond to local commands
-2. no cloud dependency for core function
-3. Step completed as expected
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+          <t>Step 1: Disable cloud connectivity
+Step 2: Send controller commands via hub
+Step 3: Monitor controller response
+Step 4: Verify local operation succeeds</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Controllers respond to local commands
+Expected Outcome 2: no cloud dependency for core function
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>REQ-072</t>
         </is>
@@ -1403,51 +1302,46 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>VER-018</t>
+          <t>VER-018: Siren Audio Alert</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Siren Audio Alert</t>
+          <t>Verify alarm siren reaches 100dB at 1m</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Verify alarm siren reaches 100dB at 1m</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Hub powered on, siren connected, sound meter available</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, siren connected, sound meter available</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1. Trigger alarm mode
-2. Measure siren output at 1 meter
-3. Verify sustained output for 30 seconds
-4. Check audio spectrum</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1. Siren output ≥100 dB SPL at 1m
-2. sustained for alarm duration
-3. Verification successful
-4. Check completed</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+          <t>Step 1: Trigger alarm mode
+Step 2: Measure siren output at 1 meter
+Step 3: Verify sustained output for 30 seconds
+Step 4: Check audio spectrum</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Siren output ≥100 dB SPL at 1m
+Expected Outcome 2: sustained for alarm duration
+Expected Outcome 3: Verification successful
+Expected Outcome 4: Check completed</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>REQ-084-085</t>
         </is>
@@ -1456,51 +1350,46 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>VER-019</t>
+          <t>VER-019: Push Notification Delivery</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Push Notification Delivery</t>
+          <t>Verify mobile app receives alerts &lt;10s on WiFi</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Verify mobile app receives alerts &lt;10s on WiFi</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, mobile app installed, WiFi active</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, mobile app installed, WiFi active</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1. Trigger motion sensor
-2. Monitor hub timestamp
-3. Monitor app notification timestamp
-4. Calculate latency</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1. Notification received &lt;10 seconds on WiFi
-2. &lt;15s on cellular
-3. Step completed as expected
-4. Step completed as expected</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+          <t>Step 1: Trigger motion sensor
+Step 2: Monitor hub timestamp
+Step 3: Monitor app notification timestamp
+Step 4: Calculate latency</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Notification received &lt;10 seconds on WiFi
+Expected Outcome 2: &lt;15s on cellular
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Step completed as expected</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>REQ-082-083</t>
         </is>
@@ -1509,51 +1398,46 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>VER-020</t>
+          <t>VER-020: Multi-User Notification</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Multi-User Notification</t>
+          <t>Verify all authorized users receive alert</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Verify all authorized users receive alert</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, 3+ users configured with different roles</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, 3+ users configured with different roles</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>1. Trigger security event
-2. Monitor notifications for each user
-3. Verify all receive alert
-4. Confirm ACL honored</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1. All authorized users receive alert
-2. unauthorized users do not
-3. Verification successful
-4. Step completed as expected</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+          <t>Step 1: Trigger security event
+Step 2: Monitor notifications for each user
+Step 3: Verify all receive alert
+Step 4: Confirm ACL honored</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: All authorized users receive alert
+Expected Outcome 2: unauthorized users do not
+Expected Outcome 3: Verification successful
+Expected Outcome 4: Step completed as expected</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>REQ-088-089</t>
         </is>
@@ -1562,55 +1446,50 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>VER-021</t>
+          <t>VER-021: Authentication MFA Verification</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Authentication MFA Verification</t>
+          <t>Verify MFA code required for admin access</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Verify MFA code required for admin access</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, MFA enabled for admin account</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, MFA enabled for admin account</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1. Attempt admin login
-2. Verify MFA prompt appears
-3. Enter invalid code
-4. Verify login denied
-5. Enter valid code
-6. Verify login succeeds</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1. Invalid MFA rejected
-2. valid MFA grants access
-3. 2 of 3 factors required
-4. Verification successful
-5. Step completed as expected
-6. Verification successful</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
+          <t>Step 1: Attempt admin login
+Step 2: Verify MFA prompt appears
+Step 3: Enter invalid code
+Step 4: Verify login denied
+Step 5: Enter valid code
+Step 6: Verify login succeeds</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Invalid MFA rejected
+Expected Outcome 2: valid MFA grants access
+Expected Outcome 3: 2 of 3 factors required
+Expected Outcome 4: Verification successful
+Expected Outcome 5: Step completed as expected
+Expected Outcome 6: Verification successful</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>REQ-100-101</t>
         </is>
@@ -1619,51 +1498,46 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>VER-022</t>
+          <t>VER-022: Role-Based Access Control</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Role-Based Access Control</t>
+          <t>Verify guest role cannot change settings</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Verify guest role cannot change settings</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, guest user account created</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, guest user account created</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as guest
-2. Attempt to change security settings
-3. Monitor audit log for unauthorized attempt
-4. Verify action blocked</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1. Guest cannot modify settings
-2. admin notified of attempt
-3. audit logged
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
+          <t>Step 1: Login as guest
+Step 2: Attempt to change security settings
+Step 3: Monitor audit log for unauthorized attempt
+Step 4: Verify action blocked</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Guest cannot modify settings
+Expected Outcome 2: admin notified of attempt
+Expected Outcome 3: audit logged
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>REQ-103-104</t>
         </is>
@@ -1672,51 +1546,46 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>VER-023</t>
+          <t>VER-023: Session Timeout</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Session Timeout</t>
+          <t>Verify remote session expires after 30 minutes</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Verify remote session expires after 30 minutes</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, user logged in remotely</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, user logged in remotely</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>1. Login to hub remotely
-2. Observe activity timeout after 30 min
-3. Monitor session log
-4. Verify re-authentication required</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>1. Session expires after 30 min inactivity
-2. re-login required
-3. no persistent connection
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
+          <t>Step 1: Login to hub remotely
+Step 2: Observe activity timeout after 30 min
+Step 3: Monitor session log
+Step 4: Verify re-authentication required</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Session expires after 30 min inactivity
+Expected Outcome 2: re-login required
+Expected Outcome 3: no persistent connection
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>REQ-105</t>
         </is>
@@ -1725,51 +1594,46 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>VER-024</t>
+          <t>VER-024: Password Complexity Enforcement</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Password Complexity Enforcement</t>
+          <t>Verify weak passwords rejected</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Verify weak passwords rejected</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, account creation enabled</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, account creation enabled</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1. Attempt password: '123456'
-2. Verify rejected
-3. Attempt: 'Secure@Pass1'
-4. Verify accepted</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1. Weak password rejected
-2. strong password accepted per NIST guidelines
-3. Step completed as expected
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
+          <t>Step 1: Attempt password: '123456'
+Step 2: Verify rejected
+Step 3: Attempt: 'Secure@Pass1'
+Step 4: Verify accepted</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Weak password rejected
+Expected Outcome 2: strong password accepted per NIST guidelines
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>REQ-102</t>
         </is>
@@ -1778,51 +1642,46 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>VER-025</t>
+          <t>VER-025: Encryption in Transit</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Encryption in Transit</t>
+          <t>Verify HTTPS/TLS 1.2 for cloud communications</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Verify HTTPS/TLS 1.2 for cloud communications</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub configured for cloud sync</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Hub configured for cloud sync</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1. Capture network traffic during cloud sync
-2. Analyze packet encryption
-3. Verify TLS 1.2+ protocol
-4. Check certificate chain</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1. All cloud traffic encrypted TLS 1.2+
-2. certificate chain valid
-3. Verification successful
-4. Check completed</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
+          <t>Step 1: Capture network traffic during cloud sync
+Step 2: Analyze packet encryption
+Step 3: Verify TLS 1.2+ protocol
+Step 4: Check certificate chain</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: All cloud traffic encrypted TLS 1.2+
+Expected Outcome 2: certificate chain valid
+Expected Outcome 3: Verification successful
+Expected Outcome 4: Check completed</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>REQ-106</t>
         </is>
@@ -1831,51 +1690,46 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>VER-026</t>
+          <t>VER-026: Data Privacy - No Logs Shared</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Data Privacy - No Logs Shared</t>
+          <t>Verify video not sent to cloud without consent</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Verify video not sent to cloud without consent</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub powered on, cloud disabled in settings</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, cloud disabled in settings</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1. Disable cloud upload setting
-2. Trigger camera recording
-3. Monitor network traffic
-4. Verify no outbound video flow</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1. No video data transmitted to cloud
-2. only metadata cached locally
-3. Step completed as expected
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
+          <t>Step 1: Disable cloud upload setting
+Step 2: Trigger camera recording
+Step 3: Monitor network traffic
+Step 4: Verify no outbound video flow</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: No video data transmitted to cloud
+Expected Outcome 2: only metadata cached locally
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>REQ-119</t>
         </is>
@@ -1884,53 +1738,48 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>VER-027</t>
+          <t>VER-027: WiFi to Cellular Failover</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>WiFi to Cellular Failover</t>
+          <t>Verify &lt;30s switchover when WiFi lost</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Verify &lt;30s switchover when WiFi lost</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Hub with WiFi and cellular, WiFi connected initially</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Hub with WiFi and cellular, WiFi connected initially</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>1. Power on hub with WiFi
-2. Disconnect WiFi (unplug router)
-3. Monitor hub connectivity state
-4. Measure time to cellular connection
-5. Verify alert sent via cellular</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>1. Failover to cellular &lt;30 seconds
-2. alert queued during transition
-3. no alert loss
-4. Step completed as expected
-5. Verification successful</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
+          <t>Step 1: Power on hub with WiFi
+Step 2: Disconnect WiFi (unplug router)
+Step 3: Monitor hub connectivity state
+Step 4: Measure time to cellular connection
+Step 5: Verify alert sent via cellular</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Failover to cellular &lt;30 seconds
+Expected Outcome 2: alert queued during transition
+Expected Outcome 3: no alert loss
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Verification successful</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>REQ-120-124</t>
         </is>
@@ -1939,51 +1788,46 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>VER-028</t>
+          <t>VER-028: LoRaWAN Radio Mesh Range</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>LoRaWAN Radio Mesh Range</t>
+          <t>Verify 500m range in open space</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Verify 500m range in open space</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Hub with LoRaWAN gateway, test sensor, open field</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Hub with LoRaWAN gateway, test sensor, open field</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>1. Deploy sensor 500m from hub
-2. Trigger sensor event
-3. Monitor hub reception
-4. Verify event detected</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>1. Sensor event received at 500m range
-2. latency &lt;1000ms
-3. Step completed as expected
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
+          <t>Step 1: Deploy sensor 500m from hub
+Step 2: Trigger sensor event
+Step 3: Monitor hub reception
+Step 4: Verify event detected</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Sensor event received at 500m range
+Expected Outcome 2: latency &lt;1000ms
+Expected Outcome 3: Step completed as expected
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>REQ-122</t>
         </is>
@@ -1992,51 +1836,46 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>VER-029</t>
+          <t>VER-029: System Health Self-Test</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>System Health Self-Test</t>
+          <t>Verify daily self-test executed and logged</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Verify daily self-test executed and logged</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Hub powered on, self-test scheduled daily at 2am</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, self-test scheduled daily at 2am</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>1. Monitor for 24 hours
-2. Observe self-test execution at scheduled time
-3. Check hub logs for test results
-4. Verify all subsystems tested</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>1. Self-test executes daily
-2. all subsystems report pass/fail
-3. logs retained
-4. Verification successful</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
+          <t>Step 1: Monitor for 24 hours
+Step 2: Observe self-test execution at scheduled time
+Step 3: Check hub logs for test results
+Step 4: Verify all subsystems tested</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Self-test executes daily
+Expected Outcome 2: all subsystems report pass/fail
+Expected Outcome 3: logs retained
+Expected Outcome 4: Verification successful</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>REQ-007</t>
         </is>
@@ -2045,59 +1884,53 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>VER-030</t>
+          <t>VER-030: Hub Boot Recovery</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Hub Boot Recovery</t>
+          <t>Verify hub resumes operation after power loss</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Verify hub resumes operation after power loss</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>non-functional</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Hub powered on, event in progress, power cut</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Hub powered on, event in progress, power cut</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>1. Power down hub during active event
-2. Wait 10 seconds
-3. Power on hub
-4. Monitor boot sequence
-5. Verify operational within 2 minutes</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>1. Hub boots successfully
-2. resumes monitoring
-3. cached events not lost
-4. Step completed as expected
-5. Verification successful</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
+          <t>Step 1: Power down hub during active event
+Step 2: Wait 10 seconds
+Step 3: Power on hub
+Step 4: Monitor boot sequence
+Step 5: Verify operational within 2 minutes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Expected Outcome 1: Hub boots successfully
+Expected Outcome 2: resumes monitoring
+Expected Outcome 3: cached events not lost
+Expected Outcome 4: Step completed as expected
+Expected Outcome 5: Verification successful</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>REQ-295</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
